--- a/external_references/approved_varroa_treatments_ireland_with_summary.xlsx
+++ b/external_references/approved_varroa_treatments_ireland_with_summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rico Zmarzly\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a7d248e1c1b7c5c/Bees/Apps/beekeeper-app/external_references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9857FFA9-3009-4D97-9D4A-E80F0FB484C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9857FFA9-3009-4D97-9D4A-E80F0FB484C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C79F2FEA-240B-4822-BD32-4FF48B06C37B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -584,19 +584,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -674,7 +674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>43</v>
       </c>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>51</v>
       </c>
@@ -864,9 +864,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="79.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>55</v>
       </c>
@@ -877,7 +887,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -900,7 +910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -926,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -952,7 +962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -978,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1004,7 +1014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1030,7 +1040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1056,7 +1066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -1082,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -1108,7 +1118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -1134,42 +1144,42 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
